--- a/Simulationen_und_Dokumentationen/Dokumentationen/Kostentabelle.xlsx
+++ b/Simulationen_und_Dokumentationen/Dokumentationen/Kostentabelle.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\Documents\Diplomarbeit\Simulationen_und_Dokumentationen\Dokumentationen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{887D8D11-36B1-4981-ACC6-96A94F83D94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B7F52B-2A84-49C5-BEDF-3AA6F429D348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1F251EE6-3B28-48B1-9445-11B12273F987}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="74">
   <si>
     <t>Website</t>
   </si>
@@ -246,6 +246,18 @@
   </si>
   <si>
     <t>mwst.</t>
+  </si>
+  <si>
+    <t>------------------------------</t>
+  </si>
+  <si>
+    <t>---------------------------------</t>
+  </si>
+  <si>
+    <t>Obi Markt</t>
+  </si>
+  <si>
+    <t>Holzplatte 20x70 cm</t>
   </si>
 </sst>
 </file>
@@ -255,7 +267,7 @@
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-1];[Red]\-#,##0.00\ [$€-1]"/>
-    <numFmt numFmtId="173" formatCode="_-[$€-C07]\ * #,##0.00_-;\-[$€-C07]\ * #,##0.00_-;_-[$€-C07]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-[$€-C07]\ * #,##0.00_-;\-[$€-C07]\ * #,##0.00_-;_-[$€-C07]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -314,7 +326,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -363,21 +375,6 @@
         <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -473,7 +470,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -481,34 +478,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyBorder="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="2" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
@@ -862,62 +858,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32"/>
-      <c r="B1" s="33" t="s">
+      <c r="A1" s="29"/>
+      <c r="B1" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="31" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26">
+      <c r="A2" s="23">
         <v>1</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="24">
         <v>1</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="26">
         <v>90.45</v>
       </c>
-      <c r="I2" s="30"/>
-      <c r="J2" s="31">
+      <c r="I2" s="27"/>
+      <c r="J2" s="28">
         <v>90.45</v>
       </c>
     </row>
@@ -1311,7 +1307,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I15" s="8"/>
-      <c r="J15" s="17">
+      <c r="J15" s="32">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -1341,46 +1337,67 @@
         <v>9.08</v>
       </c>
       <c r="I16" s="8"/>
-      <c r="J16" s="17">
+      <c r="J16" s="32">
         <v>9.08</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="13"/>
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="5">
+        <v>4</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>72</v>
+      </c>
       <c r="G17" s="14"/>
       <c r="H17" s="5"/>
-      <c r="I17" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="J17" s="20">
-        <v>10.47</v>
+      <c r="I17" s="5"/>
+      <c r="J17" s="33">
+        <v>16.96</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="21"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="25">
-        <f>SUM(J2:J17)</f>
-        <v>400.55</v>
-      </c>
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="F19" s="1"/>
       <c r="G19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="I19" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="J19" s="17">
+        <v>10.47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I20" s="21"/>
+      <c r="J20" s="22">
+        <f>SUM(J2:J19)</f>
+        <v>417.51</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B23" s="2"/>
